--- a/sample-outputs/台北A案_大明工程有限公司_20260914.xlsx
+++ b/sample-outputs/台北A案_大明工程有限公司_20260914.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3A9AD20-6849-4208-8209-7AFFCE7CB79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A57B80F-E34E-4AF5-9CC3-867CB09923BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="22440" windowHeight="15405" tabRatio="952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請款單" sheetId="23" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="109">
   <si>
     <t>合約/訂購單總額</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -403,19 +414,6 @@
   </si>
   <si>
     <t>請以匯款支付</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>台灣博世舒適科技空調設備販賣股份有限公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>銀行代碼:第一銀行(007)-城東分行
-銀行帳號: 144-10-038556</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>會館3F室外機馬達、電容損壞維修。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -426,7 +424,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -758,7 +756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -966,6 +964,278 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -976,290 +1246,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1297,7 +1283,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2002,7 +1988,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.25" style="4" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="3.75" style="4" hidden="1" customWidth="1"/>
@@ -2030,7 +2016,7 @@
     <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="7" customFormat="1" ht="36" customHeight="1">
+    <row r="1" spans="1:30" s="7" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21"/>
       <c r="C1" s="21"/>
       <c r="D1" s="12"/>
@@ -2062,7 +2048,7 @@
       <c r="AB1" s="22"/>
       <c r="AC1" s="22"/>
     </row>
-    <row r="2" spans="1:30" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:30" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5"/>
       <c r="C2" s="21"/>
       <c r="D2" s="12"/>
@@ -2095,7 +2081,7 @@
       <c r="AC2" s="142"/>
       <c r="AD2" s="142"/>
     </row>
-    <row r="3" spans="1:30" s="29" customFormat="1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:30" s="29" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
       <c r="B3" s="28"/>
       <c r="C3" s="21"/>
@@ -2108,21 +2094,29 @@
       <c r="S3" s="143"/>
       <c r="T3" s="143"/>
       <c r="U3" s="143"/>
-      <c r="V3" s="123">
+      <c r="V3" s="120">
         <v>115</v>
       </c>
-      <c r="W3" s="123"/>
+      <c r="W3" s="120"/>
       <c r="X3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="123">
+      <c r="Y3" s="120">
         <v>9</v>
       </c>
-      <c r="AB3" s="123">
+      <c r="Z3" s="120"/>
+      <c r="AA3" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB3" s="120">
         <v>14</v>
       </c>
+      <c r="AC3" s="120"/>
+      <c r="AD3" s="43" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" s="29" customFormat="1" ht="16.5" customHeight="1">
+    <row r="4" spans="1:30" s="29" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42"/>
       <c r="B4" s="37" t="s">
         <v>105</v>
@@ -2133,44 +2127,44 @@
       <c r="D4" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="117" t="s">
+      <c r="E4" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117" t="s">
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="118" t="s">
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="137" t="s">
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="134" t="s">
         <v>14</v>
       </c>
       <c r="Z4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="AA4" s="125"/>
-      <c r="AB4" s="126"/>
-      <c r="AC4" s="126"/>
-      <c r="AD4" s="127"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="123"/>
+      <c r="AC4" s="123"/>
+      <c r="AD4" s="124"/>
     </row>
-    <row r="5" spans="1:30" s="9" customFormat="1" ht="42" customHeight="1">
+    <row r="5" spans="1:30" s="9" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
         <v>16</v>
       </c>
@@ -2183,39 +2177,46 @@
       <c r="D5" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="119" t="inlineStr">
+      <c r="E5" s="116" t="inlineStr">
         <is>
           <t xml:space="preserve">台北A案</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="116" t="inlineStr">
         <is>
           <t xml:space="preserve">REQ-2026-001</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">大明工程有限公司</t>
         </is>
       </c>
-      <c r="O5" s="135"/>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="135"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="136"/>
-      <c r="Y5" s="137"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="132"/>
+      <c r="T5" s="132"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="132"/>
+      <c r="W5" s="132"/>
+      <c r="X5" s="133"/>
+      <c r="Y5" s="134"/>
       <c r="Z5" s="44"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="129"/>
-      <c r="AC5" s="129"/>
-      <c r="AD5" s="130"/>
+      <c r="AA5" s="125"/>
+      <c r="AB5" s="126"/>
+      <c r="AC5" s="126"/>
+      <c r="AD5" s="127"/>
     </row>
-    <row r="6" spans="1:30" s="29" customFormat="1" ht="16.5" customHeight="1">
+    <row r="6" spans="1:30" s="29" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
         <v>83</v>
       </c>
@@ -2228,40 +2229,40 @@
       <c r="D6" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="117" t="s">
+      <c r="E6" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117" t="s">
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="118" t="s">
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114"/>
+      <c r="N6" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="O6" s="76"/>
-      <c r="P6" s="76"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="137"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="134"/>
       <c r="Z6" s="44"/>
-      <c r="AA6" s="128"/>
-      <c r="AB6" s="129"/>
-      <c r="AC6" s="129"/>
-      <c r="AD6" s="130"/>
+      <c r="AA6" s="125"/>
+      <c r="AB6" s="126"/>
+      <c r="AC6" s="126"/>
+      <c r="AD6" s="127"/>
     </row>
-    <row r="7" spans="1:30" s="9" customFormat="1" ht="12" customHeight="1">
+    <row r="7" spans="1:30" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>82</v>
       </c>
@@ -2274,41 +2275,48 @@
       <c r="D7" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="138" t="inlineStr">
+      <c r="E7" s="135" t="inlineStr">
         <is>
           <t xml:space="preserve">工務部</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="135" t="inlineStr">
         <is>
           <t xml:space="preserve">CTR-2026-088</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="137"/>
+      <c r="N7" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">銀行代碼:007-城東分行
 戶名:大明工程有限公司
 帳號:123-456-789012</t>
         </is>
       </c>
-      <c r="O7" s="145"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
-      <c r="S7" s="145"/>
-      <c r="T7" s="145"/>
-      <c r="U7" s="145"/>
-      <c r="V7" s="145"/>
-      <c r="W7" s="145"/>
-      <c r="X7" s="146"/>
-      <c r="Y7" s="137"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="139"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="140"/>
+      <c r="Y7" s="134"/>
       <c r="Z7" s="45"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="132"/>
-      <c r="AC7" s="132"/>
-      <c r="AD7" s="133"/>
+      <c r="AA7" s="128"/>
+      <c r="AB7" s="129"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="130"/>
     </row>
-    <row r="8" spans="1:30" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:30" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>107</v>
       </c>
@@ -2321,36 +2329,36 @@
       <c r="D8" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="119"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="120"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="148"/>
-      <c r="P8" s="148"/>
-      <c r="Q8" s="148"/>
-      <c r="R8" s="148"/>
-      <c r="S8" s="148"/>
-      <c r="T8" s="148"/>
-      <c r="U8" s="148"/>
-      <c r="V8" s="148"/>
-      <c r="W8" s="148"/>
-      <c r="X8" s="149"/>
-      <c r="Y8" s="137"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="132"/>
+      <c r="P8" s="132"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" s="132"/>
+      <c r="S8" s="132"/>
+      <c r="T8" s="132"/>
+      <c r="U8" s="132"/>
+      <c r="V8" s="132"/>
+      <c r="W8" s="132"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="134"/>
       <c r="Z8" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="80"/>
-      <c r="AD8" s="81"/>
+      <c r="AA8" s="76"/>
+      <c r="AB8" s="77"/>
+      <c r="AC8" s="77"/>
+      <c r="AD8" s="78"/>
     </row>
-    <row r="9" spans="1:30" s="29" customFormat="1" ht="12" customHeight="1">
+    <row r="9" spans="1:30" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
       <c r="B9" s="37" t="s">
         <v>93</v>
@@ -2361,40 +2369,40 @@
       <c r="D9" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="117" t="s">
+      <c r="E9" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117" t="s">
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="118" t="s">
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="76"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="76"/>
-      <c r="V9" s="76"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="76"/>
-      <c r="Y9" s="137"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="73"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="134"/>
       <c r="Z9" s="44"/>
-      <c r="AA9" s="85"/>
-      <c r="AB9" s="86"/>
-      <c r="AC9" s="86"/>
-      <c r="AD9" s="87"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="84"/>
     </row>
-    <row r="10" spans="1:30" s="29" customFormat="1" ht="42" customHeight="1">
+    <row r="10" spans="1:30" s="29" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="37" t="s">
         <v>94</v>
@@ -2405,33 +2413,52 @@
       <c r="D10" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="119" t="inlineStr">
+      <c r="E10" s="116" t="inlineStr">
         <is>
-          <t xml:space="preserve">空調工程修繕款</t>
+          <t xml:space="preserve">空調工程款</t>
         </is>
       </c>
-      <c r="I10">
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="116">
         <v>500000</v>
       </c>
-      <c r="N10">
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="119">
         <v>115</v>
       </c>
-      <c r="Q10" s="123">
+      <c r="O10" s="120"/>
+      <c r="P10" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="120">
         <v>9</v>
       </c>
-      <c r="T10" s="123">
+      <c r="R10" s="120"/>
+      <c r="S10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="T10" s="120">
         <v>30</v>
       </c>
-      <c r="W10" s="90"/>
-      <c r="X10" s="91"/>
-      <c r="Y10" s="137"/>
+      <c r="U10" s="121"/>
+      <c r="V10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="W10" s="87"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="134"/>
       <c r="Z10" s="45"/>
-      <c r="AA10" s="82"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="83"/>
-      <c r="AD10" s="84"/>
+      <c r="AA10" s="79"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="80"/>
+      <c r="AD10" s="81"/>
     </row>
-    <row r="11" spans="1:30" s="9" customFormat="1" ht="14.25" customHeight="1">
+    <row r="11" spans="1:30" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="37" t="s">
         <v>95</v>
@@ -2445,47 +2472,47 @@
       <c r="E11" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="107"/>
+      <c r="G11" s="104"/>
       <c r="H11" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="108" t="s">
+      <c r="I11" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108" t="s">
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="108"/>
-      <c r="N11" s="98" t="s">
+      <c r="M11" s="105"/>
+      <c r="N11" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="100"/>
-      <c r="T11" s="111" t="s">
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="U11" s="112"/>
-      <c r="V11" s="112"/>
-      <c r="W11" s="112"/>
-      <c r="X11" s="112"/>
-      <c r="Y11" s="137"/>
+      <c r="U11" s="109"/>
+      <c r="V11" s="109"/>
+      <c r="W11" s="109"/>
+      <c r="X11" s="109"/>
+      <c r="Y11" s="134"/>
       <c r="Z11" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="80"/>
-      <c r="AC11" s="80"/>
-      <c r="AD11" s="81"/>
+      <c r="AA11" s="76"/>
+      <c r="AB11" s="77"/>
+      <c r="AC11" s="77"/>
+      <c r="AD11" s="78"/>
     </row>
-    <row r="12" spans="1:30" s="9" customFormat="1" ht="16.5" customHeight="1">
+    <row r="12" spans="1:30" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="37" t="s">
         <v>96</v>
@@ -2497,43 +2524,43 @@
         <v>57</v>
       </c>
       <c r="E12" s="64"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="107"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="104"/>
       <c r="H12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="88" t="s">
+      <c r="I12" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="88"/>
-      <c r="K12" s="88"/>
-      <c r="L12" s="88" t="s">
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="88"/>
-      <c r="N12" s="89" t="s">
+      <c r="M12" s="85"/>
+      <c r="N12" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="89" t="s">
+      <c r="O12" s="87"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="U12" s="90"/>
-      <c r="V12" s="90"/>
-      <c r="W12" s="90"/>
-      <c r="X12" s="90"/>
-      <c r="Y12" s="137"/>
+      <c r="U12" s="87"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="87"/>
+      <c r="X12" s="87"/>
+      <c r="Y12" s="134"/>
       <c r="Z12" s="44"/>
-      <c r="AA12" s="85"/>
-      <c r="AB12" s="86"/>
-      <c r="AC12" s="86"/>
-      <c r="AD12" s="87"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="83"/>
+      <c r="AC12" s="83"/>
+      <c r="AD12" s="84"/>
     </row>
-    <row r="13" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1">
+    <row r="13" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="37" t="s">
         <v>97</v>
@@ -2549,36 +2576,42 @@
         <v>40</v>
       </c>
       <c r="G13" s="58"/>
-      <c r="H13" s="109">
+      <c r="H13" s="106">
         <v>120000</v>
       </c>
-      <c r="I13" s="92"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="94"/>
-      <c r="T13" s="101">
+      <c r="I13" s="89">
+        <v>12000</v>
+      </c>
+      <c r="J13" s="90"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="89">
+        <v>0</v>
+      </c>
+      <c r="M13" s="91"/>
+      <c r="N13" s="89">
+        <v>0</v>
+      </c>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="98">
         <f>H13-I13-L13-N13</f>
-        <v>14999</v>
-      </c>
-      <c r="U13" s="102"/>
-      <c r="V13" s="102"/>
-      <c r="W13" s="102"/>
-      <c r="X13" s="103"/>
-      <c r="Y13" s="137"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="99"/>
+      <c r="V13" s="99"/>
+      <c r="W13" s="99"/>
+      <c r="X13" s="100"/>
+      <c r="Y13" s="134"/>
       <c r="Z13" s="44"/>
-      <c r="AA13" s="85"/>
-      <c r="AB13" s="86"/>
-      <c r="AC13" s="86"/>
-      <c r="AD13" s="87"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="84"/>
     </row>
-    <row r="14" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1">
+    <row r="14" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="37" t="s">
         <v>98</v>
@@ -2590,35 +2623,35 @@
         <v>59</v>
       </c>
       <c r="E14" s="64"/>
-      <c r="F14" s="113" t="s">
+      <c r="F14" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="114"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="97"/>
-      <c r="T14" s="104"/>
-      <c r="U14" s="105"/>
-      <c r="V14" s="105"/>
-      <c r="W14" s="105"/>
-      <c r="X14" s="106"/>
-      <c r="Y14" s="137"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="94"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="93"/>
+      <c r="P14" s="93"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="102"/>
+      <c r="X14" s="103"/>
+      <c r="Y14" s="134"/>
       <c r="Z14" s="44"/>
-      <c r="AA14" s="85"/>
-      <c r="AB14" s="86"/>
-      <c r="AC14" s="86"/>
-      <c r="AD14" s="87"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="83"/>
+      <c r="AC14" s="83"/>
+      <c r="AD14" s="84"/>
     </row>
-    <row r="15" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1">
+    <row r="15" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="37" t="s">
         <v>99</v>
@@ -2630,38 +2663,38 @@
         <v>60</v>
       </c>
       <c r="E15" s="64"/>
-      <c r="F15" s="115" t="s">
+      <c r="F15" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="116"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="93"/>
-      <c r="S15" s="94"/>
-      <c r="T15" s="101">
+      <c r="G15" s="113"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="90"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="90"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="91"/>
+      <c r="T15" s="98">
         <f>H16-I16-L16-N16</f>
         <v>0</v>
       </c>
-      <c r="U15" s="102"/>
-      <c r="V15" s="102"/>
-      <c r="W15" s="102"/>
-      <c r="X15" s="103"/>
-      <c r="Y15" s="137"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="100"/>
+      <c r="Y15" s="134"/>
       <c r="Z15" s="44"/>
-      <c r="AA15" s="85"/>
-      <c r="AB15" s="86"/>
-      <c r="AC15" s="86"/>
-      <c r="AD15" s="87"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="83"/>
+      <c r="AC15" s="83"/>
+      <c r="AD15" s="84"/>
     </row>
-    <row r="16" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1">
+    <row r="16" spans="1:30" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="37" t="s">
         <v>100</v>
@@ -2675,31 +2708,31 @@
         <v>41</v>
       </c>
       <c r="G16" s="45"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="97"/>
-      <c r="T16" s="104"/>
-      <c r="U16" s="105"/>
-      <c r="V16" s="105"/>
-      <c r="W16" s="105"/>
-      <c r="X16" s="106"/>
-      <c r="Y16" s="137"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="93"/>
+      <c r="Q16" s="93"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="94"/>
+      <c r="T16" s="101"/>
+      <c r="U16" s="102"/>
+      <c r="V16" s="102"/>
+      <c r="W16" s="102"/>
+      <c r="X16" s="103"/>
+      <c r="Y16" s="134"/>
       <c r="Z16" s="45"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="83"/>
-      <c r="AC16" s="83"/>
-      <c r="AD16" s="84"/>
+      <c r="AA16" s="79"/>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="81"/>
     </row>
-    <row r="17" spans="1:30" s="9" customFormat="1" ht="33" customHeight="1">
+    <row r="17" spans="1:30" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="37" t="s">
         <v>101</v>
@@ -2708,48 +2741,48 @@
       <c r="D17" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="77" t="s">
+      <c r="E17" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="77"/>
+      <c r="F17" s="74"/>
       <c r="G17" s="14" t="s">
         <v>11</v>
       </c>
       <c r="H17" s="23"/>
-      <c r="I17" s="75" t="s">
+      <c r="I17" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="75" t="s">
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="N17" s="79"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="80"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="75" t="s">
+      <c r="N17" s="76"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="77"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="U17" s="68" t="s">
+      <c r="U17" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="V17" s="69"/>
-      <c r="W17" s="69"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="72" t="s">
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="Z17" s="73"/>
-      <c r="AA17" s="73"/>
-      <c r="AB17" s="73"/>
-      <c r="AC17" s="73"/>
-      <c r="AD17" s="73"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
     </row>
-    <row r="18" spans="1:30" s="9" customFormat="1" ht="33" customHeight="1">
+    <row r="18" spans="1:30" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21"/>
       <c r="B18" s="37" t="s">
         <v>102</v>
@@ -2758,36 +2791,36 @@
       <c r="D18" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="23"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="83"/>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="75"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="71"/>
-      <c r="W18" s="71"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="72"/>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="73"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="73"/>
-      <c r="AD18" s="73"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="68"/>
+      <c r="W18" s="68"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
     </row>
-    <row r="19" spans="1:30" s="9" customFormat="1" ht="2.25" customHeight="1">
+    <row r="19" spans="1:30" s="9" customFormat="1" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
       <c r="B19" s="37" t="s">
         <v>103</v>
@@ -2796,34 +2829,34 @@
       <c r="D19" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="74"/>
-      <c r="T19" s="74"/>
-      <c r="U19" s="74"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="74"/>
-      <c r="X19" s="74"/>
-      <c r="Y19" s="74"/>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="74"/>
-      <c r="AB19" s="74"/>
-      <c r="AC19" s="74"/>
-      <c r="AD19" s="74"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="71"/>
+      <c r="X19" s="71"/>
+      <c r="Y19" s="71"/>
+      <c r="Z19" s="71"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="71"/>
+      <c r="AC19" s="71"/>
+      <c r="AD19" s="71"/>
     </row>
-    <row r="20" spans="1:30" s="9" customFormat="1" ht="17.25" customHeight="1">
+    <row r="20" spans="1:30" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21"/>
       <c r="B20" s="37" t="s">
         <v>104</v>
@@ -2835,7 +2868,7 @@
       <c r="E20" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="72" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="34"/>
@@ -2843,27 +2876,27 @@
         <v>38</v>
       </c>
       <c r="I20" s="33"/>
-      <c r="J20" s="76" t="s">
+      <c r="J20" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
       <c r="N20" s="33"/>
-      <c r="O20" s="76" t="s">
+      <c r="O20" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="P20" s="76"/>
-      <c r="Q20" s="76"/>
-      <c r="R20" s="76"/>
-      <c r="S20" s="76"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="73"/>
       <c r="T20" s="33"/>
-      <c r="U20" s="76" t="s">
+      <c r="U20" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="V20" s="76"/>
-      <c r="W20" s="76"/>
-      <c r="X20" s="76"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
       <c r="Y20" s="58" t="s">
         <v>35</v>
       </c>
@@ -2873,7 +2906,7 @@
       <c r="AC20" s="60"/>
       <c r="AD20" s="61"/>
     </row>
-    <row r="21" spans="1:30" s="9" customFormat="1" ht="15.75" customHeight="1">
+    <row r="21" spans="1:30" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21"/>
       <c r="B21" s="12"/>
       <c r="C21" s="21"/>
@@ -2881,7 +2914,7 @@
         <v>68</v>
       </c>
       <c r="E21" s="64"/>
-      <c r="F21" s="75"/>
+      <c r="F21" s="72"/>
       <c r="G21" s="25"/>
       <c r="H21" s="13" t="s">
         <v>13</v>
@@ -2893,17 +2926,23 @@
       <c r="K21" s="62"/>
       <c r="L21" s="62"/>
       <c r="M21" s="62"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="32">
+      <c r="N21" s="35">
         <v>115</v>
       </c>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="32">
+      <c r="O21" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="35">
         <v>10</v>
       </c>
-      <c r="R21" s="35"/>
-      <c r="S21" s="32">
+      <c r="Q21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="R21" s="35">
         <v>15</v>
+      </c>
+      <c r="S21" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="T21" s="63" t="s">
         <v>19</v>
@@ -2919,7 +2958,7 @@
       <c r="AC21" s="47"/>
       <c r="AD21" s="48"/>
     </row>
-    <row r="22" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="22" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21"/>
       <c r="B22" s="12"/>
       <c r="C22" s="21"/>
@@ -2930,28 +2969,28 @@
       <c r="F22" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="65" t="inlineStr">
+      <c r="G22" s="144" t="inlineStr">
         <is>
           <t xml:space="preserve">1. 本期空調室外機馬達更換工程款。</t>
         </is>
       </c>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="67"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="145"/>
+      <c r="O22" s="145"/>
+      <c r="P22" s="145"/>
+      <c r="Q22" s="145"/>
+      <c r="R22" s="145"/>
+      <c r="S22" s="145"/>
+      <c r="T22" s="145"/>
+      <c r="U22" s="145"/>
+      <c r="V22" s="145"/>
+      <c r="W22" s="145"/>
+      <c r="X22" s="146"/>
       <c r="Y22" s="44"/>
       <c r="Z22" s="46"/>
       <c r="AA22" s="47"/>
@@ -2959,7 +2998,7 @@
       <c r="AC22" s="47"/>
       <c r="AD22" s="48"/>
     </row>
-    <row r="23" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="23" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21"/>
       <c r="B23" s="12"/>
       <c r="C23" s="21"/>
@@ -2997,7 +3036,7 @@
       <c r="AC23" s="47"/>
       <c r="AD23" s="48"/>
     </row>
-    <row r="24" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="24" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12"/>
       <c r="C24" s="21"/>
       <c r="D24" s="39" t="s">
@@ -3030,7 +3069,7 @@
       <c r="AC24" s="47"/>
       <c r="AD24" s="48"/>
     </row>
-    <row r="25" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="25" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21"/>
       <c r="B25" s="12"/>
       <c r="C25" s="21"/>
@@ -3064,7 +3103,7 @@
       <c r="AC25" s="50"/>
       <c r="AD25" s="51"/>
     </row>
-    <row r="26" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="26" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="21"/>
@@ -3074,13 +3113,33 @@
       <c r="E26" s="64"/>
       <c r="F26" s="64"/>
       <c r="G26" s="52"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="53"/>
+      <c r="X26" s="54"/>
+      <c r="Y26" s="58" t="s">
+        <v>47</v>
+      </c>
       <c r="Z26" s="59"/>
       <c r="AA26" s="60"/>
       <c r="AB26" s="60"/>
       <c r="AC26" s="60"/>
       <c r="AD26" s="61"/>
     </row>
-    <row r="27" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="27" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21"/>
       <c r="B27" s="12"/>
       <c r="C27" s="21"/>
@@ -3114,7 +3173,7 @@
       <c r="AC27" s="47"/>
       <c r="AD27" s="48"/>
     </row>
-    <row r="28" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="28" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21"/>
       <c r="B28" s="12"/>
       <c r="C28" s="21"/>
@@ -3148,7 +3207,7 @@
       <c r="AC28" s="47"/>
       <c r="AD28" s="48"/>
     </row>
-    <row r="29" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="29" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21"/>
       <c r="B29" s="12"/>
       <c r="C29" s="21"/>
@@ -3182,7 +3241,7 @@
       <c r="AC29" s="47"/>
       <c r="AD29" s="48"/>
     </row>
-    <row r="30" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="30" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21"/>
       <c r="B30" s="12"/>
       <c r="C30" s="21"/>
@@ -3216,7 +3275,7 @@
       <c r="AC30" s="47"/>
       <c r="AD30" s="48"/>
     </row>
-    <row r="31" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="31" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
       <c r="B31" s="12"/>
       <c r="C31" s="21"/>
@@ -3250,7 +3309,7 @@
       <c r="AC31" s="50"/>
       <c r="AD31" s="51"/>
     </row>
-    <row r="32" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="32" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21"/>
       <c r="B32" s="12"/>
       <c r="C32" s="21"/>
@@ -3260,13 +3319,33 @@
       <c r="E32" s="64"/>
       <c r="F32" s="64"/>
       <c r="G32" s="52"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
+      <c r="U32" s="53"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="53"/>
+      <c r="X32" s="54"/>
+      <c r="Y32" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="Z32" s="46"/>
       <c r="AA32" s="47"/>
       <c r="AB32" s="47"/>
       <c r="AC32" s="47"/>
       <c r="AD32" s="48"/>
     </row>
-    <row r="33" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="33" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21"/>
       <c r="B33" s="12"/>
       <c r="C33" s="21"/>
@@ -3300,7 +3379,7 @@
       <c r="AC33" s="47"/>
       <c r="AD33" s="48"/>
     </row>
-    <row r="34" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="34" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21"/>
       <c r="B34" s="12"/>
       <c r="C34" s="21"/>
@@ -3334,7 +3413,7 @@
       <c r="AC34" s="47"/>
       <c r="AD34" s="48"/>
     </row>
-    <row r="35" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="35" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21"/>
       <c r="B35" s="12"/>
       <c r="C35" s="21"/>
@@ -3366,7 +3445,7 @@
       <c r="AC35" s="47"/>
       <c r="AD35" s="48"/>
     </row>
-    <row r="36" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="36" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="21"/>
       <c r="B36" s="12"/>
       <c r="C36" s="21"/>
@@ -3398,7 +3477,7 @@
       <c r="AC36" s="47"/>
       <c r="AD36" s="48"/>
     </row>
-    <row r="37" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1">
+    <row r="37" spans="1:30" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21"/>
       <c r="B37" s="12"/>
       <c r="C37" s="21"/>
@@ -3430,7 +3509,7 @@
       <c r="AC37" s="50"/>
       <c r="AD37" s="51"/>
     </row>
-    <row r="38" spans="1:30" s="16" customFormat="1">
+    <row r="38" spans="1:30" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -3451,12 +3530,82 @@
     <protectedRange sqref="E5 I5 N5 E7 I7 N7 E10 I10 N10 I13:I16 L13:L16 N13:N16 G11 H13:H18 I20:I21 T20 N20:N21 P21 R21 Y3 AB3 U3 G20:G37" name="範圍1"/>
   </protectedRanges>
   <mergeCells count="98">
-    <mergeCell ref="H1:Y1"/>
-    <mergeCell ref="E2:AD2"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="Y32:Y37"/>
+    <mergeCell ref="Z32:AD37"/>
+    <mergeCell ref="G33:X33"/>
+    <mergeCell ref="G34:X34"/>
+    <mergeCell ref="G35:X35"/>
+    <mergeCell ref="G36:X36"/>
+    <mergeCell ref="G37:X37"/>
+    <mergeCell ref="Y26:Y31"/>
+    <mergeCell ref="Z26:AD31"/>
+    <mergeCell ref="G27:X27"/>
+    <mergeCell ref="G28:X28"/>
+    <mergeCell ref="G29:X29"/>
+    <mergeCell ref="G30:X30"/>
+    <mergeCell ref="G31:X31"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="F22:F37"/>
+    <mergeCell ref="G22:X22"/>
+    <mergeCell ref="G23:X23"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="G25:X25"/>
+    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="G32:X32"/>
+    <mergeCell ref="U17:X18"/>
+    <mergeCell ref="Y17:AD18"/>
+    <mergeCell ref="E19:AD19"/>
+    <mergeCell ref="E20:E37"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="Y20:Y25"/>
+    <mergeCell ref="Z20:AD25"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="J17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="AA11:AD16"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="I13:K14"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="N13:S14"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="T13:X14"/>
+    <mergeCell ref="I15:K16"/>
+    <mergeCell ref="L15:M16"/>
+    <mergeCell ref="N15:S16"/>
+    <mergeCell ref="T15:X16"/>
+    <mergeCell ref="Z8:Z10"/>
+    <mergeCell ref="E11:E16"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Z11:Z16"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:M9"/>
+    <mergeCell ref="N9:X9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="W10:X10"/>
     <mergeCell ref="AA4:AD7"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:M5"/>
@@ -3473,82 +3622,12 @@
     <mergeCell ref="I7:M8"/>
     <mergeCell ref="N7:X8"/>
     <mergeCell ref="AA8:AD10"/>
-    <mergeCell ref="N9:X9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Z8:Z10"/>
-    <mergeCell ref="E11:E16"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Z11:Z16"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:M9"/>
-    <mergeCell ref="AA11:AD16"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="I13:K14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="N13:S14"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="T13:X14"/>
-    <mergeCell ref="I15:K16"/>
-    <mergeCell ref="L15:M16"/>
-    <mergeCell ref="N15:S16"/>
-    <mergeCell ref="T15:X16"/>
-    <mergeCell ref="U17:X18"/>
-    <mergeCell ref="Y17:AD18"/>
-    <mergeCell ref="E19:AD19"/>
-    <mergeCell ref="E20:E37"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="Y20:Y25"/>
-    <mergeCell ref="Z20:AD25"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="J17:L18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="F22:F37"/>
-    <mergeCell ref="G22:X22"/>
-    <mergeCell ref="G23:X23"/>
-    <mergeCell ref="G24:X24"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="G26:X26"/>
-    <mergeCell ref="G32:X32"/>
-    <mergeCell ref="Y26:Y31"/>
-    <mergeCell ref="Z26:AD31"/>
-    <mergeCell ref="G27:X27"/>
-    <mergeCell ref="G28:X28"/>
-    <mergeCell ref="G29:X29"/>
-    <mergeCell ref="G30:X30"/>
-    <mergeCell ref="G31:X31"/>
-    <mergeCell ref="Y32:Y37"/>
-    <mergeCell ref="Z32:AD37"/>
-    <mergeCell ref="G33:X33"/>
-    <mergeCell ref="G34:X34"/>
-    <mergeCell ref="G35:X35"/>
-    <mergeCell ref="G36:X36"/>
-    <mergeCell ref="G37:X37"/>
+    <mergeCell ref="H1:Y1"/>
+    <mergeCell ref="E2:AD2"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AB3:AC3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
